--- a/web/public/forms/orig/o-ascon-jageop.xlsx
+++ b/web/public/forms/orig/o-ascon-jageop.xlsx
@@ -4,9 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\기계교 전술교육단 관련\토목 자료\"/>
-    </mc:Choice>
+    <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11625"/>
@@ -361,7 +359,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2" descr="C:\Users\Canon\AppData\Local\Packages\Microsoft.Windows.Photos_8wekyb3d8bbwe\TempState\ShareServiceTempFolder\20240703_183452.jpeg">
+        <xdr:cNvPr id="3" name="그림 2" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>

--- a/web/public/forms/orig/o-ascon-jageop.xlsx
+++ b/web/public/forms/orig/o-ascon-jageop.xlsx
@@ -804,7 +804,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="35" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="35" t="inlineStr">

--- a/web/public/forms/orig/o-ascon-jageop.xlsx
+++ b/web/public/forms/orig/o-ascon-jageop.xlsx
@@ -9,14 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계획서" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시공순서도" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-계획서" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-시공순서도" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'계획서'!$A$1:$E$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'시공순서도'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'예시-계획서'!$A$1:$E$63</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'예시-시공순서도'!$A$1:$L$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -277,9 +273,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -388,91 +381,6 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>38100</colOff>
-      <row>3</row>
-      <rowOff>9525</rowOff>
-    </from>
-    <ext cx="7924800" cy="5276850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>57150</colOff>
-      <row>38</row>
-      <rowOff>57150</rowOff>
-    </from>
-    <ext cx="3352800" cy="1543050"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>57150</colOff>
-      <row>49</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <ext cx="6419850" cy="2895600"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -836,10 +744,7 @@
       </c>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="7">
-        <f>IF(N(B4)=0,"",YEAR(B4)&amp;". "&amp;MONTH(B4)&amp;". "&amp;DAY(B4)&amp;".("&amp;CHOOSE(WEEKDAY(B4),"일","월","화","수","목","금","토")&amp;")"&amp;IF(N(C4)=0,""," ~ "&amp;MONTH(C4)&amp;". "&amp;DAY(C4)&amp;".("&amp;CHOOSE(WEEKDAY(C4),"일","월","화","수","목","금","토")&amp;") · "&amp;(C4-B4+1)&amp;"일"))</f>
-        <v/>
-      </c>
+      <c r="D4" s="7" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -891,10 +796,7 @@
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="12">
-        <f>IF(N(B4)=0,"",MONTH(B4)&amp;"월 "&amp;DAY(B4)&amp;"일"&amp;CHAR(10)&amp;"("&amp;CHOOSE(WEEKDAY(B4),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
+      <c r="A9" s="12" t="n"/>
       <c r="B9" s="13" t="n"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
@@ -906,10 +808,7 @@
           <t>스키로더, 콤비 3.5ton</t>
         </is>
       </c>
-      <c r="E9" s="12">
-        <f>IF(N(D26)=0,"","(당일 포장거리 "&amp;B26&amp;"m)"&amp;CHAR(10)&amp;"기층 "&amp;D26&amp;"ton"&amp;CHAR(10)&amp;"덤프 "&amp;E26&amp;"대분")</f>
-        <v/>
-      </c>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="16" t="n"/>
@@ -982,10 +881,7 @@
       <c r="E15" s="16" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="12">
-        <f>IF(OR(N(B4)=0,N(C4)&lt;=B4),"",MONTH(B4+1)&amp;"월 "&amp;DAY(B4+1)&amp;"일"&amp;CHAR(10)&amp;"("&amp;CHOOSE(WEEKDAY(B4+1),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
+      <c r="A16" s="12" t="n"/>
       <c r="B16" s="13" t="n"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
@@ -997,10 +893,7 @@
           <t>스키로더, 콤비 3.5ton</t>
         </is>
       </c>
-      <c r="E16" s="12">
-        <f>IF(N(D28)=0,"","(당일 포장거리 "&amp;B28&amp;"m)"&amp;CHAR(10)&amp;"기층 "&amp;D28&amp;"ton"&amp;CHAR(10)&amp;"덤프 "&amp;E28&amp;"대분")</f>
-        <v/>
-      </c>
+      <c r="E16" s="12" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="16" t="n"/>
@@ -1115,14 +1008,8 @@
       </c>
       <c r="B26" s="18" t="n"/>
       <c r="C26" s="19" t="n"/>
-      <c r="D26" s="20">
-        <f>IF(OR(N(B26)=0,N(B27)=0,N(C26)=0),"",ROUND(B26*B27*C26/1000*C30,1))</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>IF(OR(D26="",N(E30)=0),"",ROUNDUP(D26/E30,0))</f>
-        <v/>
-      </c>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="22" t="inlineStr"/>
@@ -1139,14 +1026,8 @@
       </c>
       <c r="B28" s="18" t="n"/>
       <c r="C28" s="19" t="n"/>
-      <c r="D28" s="20">
-        <f>IF(OR(N(B28)=0,N(B29)=0,N(C28)=0),"",ROUND(B28*B29*C28/1000*C30,1))</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>IF(OR(D28="",N(E30)=0),"",ROUNDUP(D28/E30,0))</f>
-        <v/>
-      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="21" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="22" t="inlineStr"/>
@@ -1286,10 +1167,7 @@
           <t>합  계</t>
         </is>
       </c>
-      <c r="E44" s="30">
-        <f>IF(SUM(E39:E43)=0,"",SUM(E39:E43))</f>
-        <v/>
-      </c>
+      <c r="E44" s="30" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="27" t="inlineStr">
@@ -1422,6 +1300,7 @@
       <c r="D63" s="16" t="n"/>
       <c r="E63" s="16" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="33" t="inlineStr">
         <is>
@@ -1553,720 +1432,7 @@
     <row r="24" ht="19" customHeight="1"/>
     <row r="25" ht="19" customHeight="1"/>
     <row r="26" ht="19" customHeight="1"/>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>원본 계획서의 시공순서도 그림입니다(참고용).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A28:L28"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="D1" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>아스콘 포장 작업 계획서</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>□ 공 사 명</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>□ 작 업 일</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>46207</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>46208</v>
-      </c>
-      <c r="D4" s="7">
-        <f>IF(N(B4)=0,"",YEAR(B4)&amp;". "&amp;MONTH(B4)&amp;". "&amp;DAY(B4)&amp;".("&amp;CHOOSE(WEEKDAY(B4),"일","월","화","수","목","금","토")&amp;")"&amp;IF(N(C4)=0,""," ~ "&amp;MONTH(C4)&amp;". "&amp;DAY(C4)&amp;".("&amp;CHOOSE(WEEKDAY(C4),"일","월","화","수","목","금","토")&amp;") · "&amp;(C4-B4+1)&amp;"일"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>□ 작업 책임자</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>현장소장</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr"/>
-    </row>
-    <row r="6" ht="6" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>□ 아스콘포장 작업 및 장비 투입계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>일  자</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>작 업 구 간</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>구  분</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>장비 및 인원 투입계획</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="12">
-        <f>IF(N(B4)=0,"",MONTH(B4)&amp;"월 "&amp;DAY(B4)&amp;"일"&amp;CHAR(10)&amp;"("&amp;CHOOSE(WEEKDAY(B4),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>JG-400-011 ~ JG-400-001</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>아스콘포장 장비 및 인원</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>스키로더, 콤비 3.5ton</t>
-        </is>
-      </c>
-      <c r="E9" s="12">
-        <f>IF(N(D26)=0,"","(당일 포장거리 "&amp;B26&amp;"m)"&amp;CHAR(10)&amp;"기층 "&amp;D26&amp;"ton"&amp;CHAR(10)&amp;"덤프 "&amp;E26&amp;"대분")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>디스트리뷰터 1.0ton</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n"/>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>포장공 3인</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>포장토공 장비 및 인원</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>덤프 15ton 2대</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n"/>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="16" t="n"/>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>백호 0.6㎥ 3대</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="16" t="n"/>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>신호수 2명</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="16" t="n"/>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>보통인부 4명</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="12">
-        <f>IF(OR(N(B4)=0,N(C4)&lt;=B4),"",MONTH(B4+1)&amp;"월 "&amp;DAY(B4+1)&amp;"일"&amp;CHAR(10)&amp;"("&amp;CHOOSE(WEEKDAY(B4+1),"일","월","화","수","목","금","토")&amp;")")</f>
-        <v/>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>SGP-100-01 NO.4 ~ NO.34</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>아스콘포장 장비 및 인원</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>스키로더, 콤비 3.5ton</t>
-        </is>
-      </c>
-      <c r="E16" s="12">
-        <f>IF(N(D28)=0,"","(당일 포장거리 "&amp;B28&amp;"m)"&amp;CHAR(10)&amp;"기층 "&amp;D28&amp;"ton"&amp;CHAR(10)&amp;"덤프 "&amp;E28&amp;"대분")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="16" t="n"/>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>디스트리뷰터 1.0ton</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="16" t="n"/>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>포장공 3인</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="16" t="n"/>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>포장토공 장비 및 인원</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>덤프 15ton 2대</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="16" t="n"/>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>백호 0.6㎥ 3대</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="16" t="n"/>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>신호수 2명</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="16" t="n"/>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>보통인부 4명</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="8" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>□ 아스콘 물량 · 운반 계산</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>일  자</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>포장거리(m) · 폭(m)</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>두께(mm)</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>아스콘 물량(ton)</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>덤프 대수</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>1일째</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="C26" s="19" t="n">
-        <v>150</v>
-      </c>
-      <c r="D26" s="20">
-        <f>IF(OR(N(B26)=0,N(B27)=0,N(C26)=0),"",ROUND(B26*B27*C26/1000*C30,1))</f>
-        <v/>
-      </c>
-      <c r="E26" s="21">
-        <f>IF(OR(D26="",N(E30)=0),"",ROUNDUP(D26/E30,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="22" t="inlineStr"/>
-      <c r="B27" s="23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C27" s="22" t="inlineStr"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>2일째</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="n">
-        <v>700</v>
-      </c>
-      <c r="C28" s="19" t="n">
-        <v>150</v>
-      </c>
-      <c r="D28" s="20">
-        <f>IF(OR(N(B28)=0,N(B29)=0,N(C28)=0),"",ROUND(B28*B29*C28/1000*C30,1))</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>IF(OR(D28="",N(E30)=0),"",ROUNDUP(D28/E30,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="22" t="inlineStr"/>
-      <c r="B29" s="23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C29" s="22" t="inlineStr"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>기준값</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>아스콘 밀도</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>덤프 1대 적재</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" ht="8" customHeight="1"/>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>□ 아스콘포장 작업순서</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1) 가포장 보조기층 걷어내기(T=200) : B/H 0.6㎥, D/T 15ton</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2) 보조기층 다짐 : 1ton 롤러</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 3) 프라임 코팅 살포 : 디스트리뷰터 1.0ton</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 4) 기층 포설 및 다짐(기층 T=150) : 스키로더, 콤비 3.5ton</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 5) 추후 가포장 임시 도장(임시포장)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>□ 아스콘포장 단면도</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="9" t="inlineStr"/>
-      <c r="D39" s="14" t="inlineStr">
-        <is>
-          <t>표층</t>
-        </is>
-      </c>
-      <c r="E39" s="28" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>택 코팅</t>
-        </is>
-      </c>
-      <c r="E40" s="28" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>기층</t>
-        </is>
-      </c>
-      <c r="E41" s="28" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr"/>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>프라임 코팅</t>
-        </is>
-      </c>
-      <c r="E42" s="28" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>보조기층</t>
-        </is>
-      </c>
-      <c r="E43" s="28" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr"/>
-      <c r="D44" s="29" t="inlineStr">
-        <is>
-          <t>합  계</t>
-        </is>
-      </c>
-      <c r="E44" s="30">
-        <f>IF(SUM(E39:E43)=0,"",SUM(E39:E43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>※ 표층(T=50)은 포장절삭 후 전면포장 예정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1"/>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
-        <is>
-          <t>보조기층 걷어내기 및 다짐 전경</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1"/>
-    <row r="49" ht="20" customHeight="1"/>
-    <row r="50" ht="20" customHeight="1"/>
-    <row r="51" ht="20" customHeight="1"/>
-    <row r="52" ht="20" customHeight="1"/>
-    <row r="53" ht="20" customHeight="1"/>
-    <row r="54" ht="20" customHeight="1"/>
-    <row r="55" ht="20" customHeight="1"/>
-    <row r="56" ht="20" customHeight="1"/>
-    <row r="57" ht="20" customHeight="1"/>
-    <row r="58" ht="20" customHeight="1"/>
-    <row r="59" ht="20" customHeight="1"/>
-    <row r="60" ht="20" customHeight="1"/>
-    <row r="61" ht="20" customHeight="1"/>
-    <row r="62" ht="20" customHeight="1"/>
-    <row r="63" ht="20" customHeight="1"/>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="33" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사). 사진은 원본 계획서의 참고 사진입니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="36">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="E9:E15"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="E16:E22"/>
-    <mergeCell ref="B16:B22"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A9:A15"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C9:C11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="37" min="0" max="16383" man="1"/>
-  </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>포 장 시 공 순 서 도</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1"/>
-    <row r="4" ht="19" customHeight="1"/>
-    <row r="5" ht="19" customHeight="1"/>
-    <row r="6" ht="19" customHeight="1"/>
-    <row r="7" ht="19" customHeight="1"/>
-    <row r="8" ht="19" customHeight="1"/>
-    <row r="9" ht="19" customHeight="1"/>
-    <row r="10" ht="19" customHeight="1"/>
-    <row r="11" ht="19" customHeight="1"/>
-    <row r="12" ht="19" customHeight="1"/>
-    <row r="13" ht="19" customHeight="1"/>
-    <row r="14" ht="19" customHeight="1"/>
-    <row r="15" ht="19" customHeight="1"/>
-    <row r="16" ht="19" customHeight="1"/>
-    <row r="17" ht="19" customHeight="1"/>
-    <row r="18" ht="19" customHeight="1"/>
-    <row r="19" ht="19" customHeight="1"/>
-    <row r="20" ht="19" customHeight="1"/>
-    <row r="21" ht="19" customHeight="1"/>
-    <row r="22" ht="19" customHeight="1"/>
-    <row r="23" ht="19" customHeight="1"/>
-    <row r="24" ht="19" customHeight="1"/>
-    <row r="25" ht="19" customHeight="1"/>
-    <row r="26" ht="19" customHeight="1"/>
+    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="33" t="inlineStr">
         <is>

--- a/web/public/forms/orig/o-ascon-jageop.xlsx
+++ b/web/public/forms/orig/o-ascon-jageop.xlsx
@@ -712,7 +712,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
